--- a/Result/profitability/6208.xlsx
+++ b/Result/profitability/6208.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.22</v>
       </c>
       <c r="M2" t="n">
-        <v>0.7687499999999999</v>
+        <v>0.83375</v>
       </c>
       <c r="N2" t="n">
-        <v>32.83375</v>
+        <v>32.0125</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.41</v>
       </c>
       <c r="M3" t="n">
-        <v>0.7324999999999999</v>
+        <v>0.7837499999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>32.41375</v>
+        <v>31.6675</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.49</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6925</v>
+        <v>0.7675</v>
       </c>
       <c r="N4" t="n">
-        <v>32.1775</v>
+        <v>31.18375</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.34</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5725</v>
+        <v>0.6287499999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>30.19125</v>
+        <v>29.55</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.04</v>
       </c>
       <c r="M6" t="n">
-        <v>0.48125</v>
+        <v>0.585</v>
       </c>
       <c r="N6" t="n">
-        <v>29.60875</v>
+        <v>29.14125</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.37</v>
       </c>
       <c r="M7" t="n">
-        <v>0.38625</v>
+        <v>0.44625</v>
       </c>
       <c r="N7" t="n">
-        <v>27.9575</v>
+        <v>27.245</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.19</v>
       </c>
       <c r="M8" t="n">
-        <v>0.27</v>
+        <v>0.185</v>
       </c>
       <c r="N8" t="n">
-        <v>27.44875</v>
+        <v>26.72125</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6208</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1011</v>
+      </c>
+      <c r="D75" t="n">
+        <v>730</v>
+      </c>
+      <c r="E75" t="n">
+        <v>281</v>
+      </c>
+      <c r="F75" t="n">
+        <v>27.77</v>
+      </c>
+      <c r="G75" t="n">
+        <v>89</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>8.82%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>37</v>
+      </c>
+      <c r="J75" t="n">
+        <v>126</v>
+      </c>
+      <c r="K75" t="n">
+        <v>115</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.8937499999999999</v>
+      </c>
+      <c r="N75" t="n">
+        <v>32.88</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.6799999999999999</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.3578947368421053</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-5.820000000000004</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.1732658529324205</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.5844155844155843</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-5.129999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.1559270516717325</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
